--- a/results/NMI.xlsx
+++ b/results/NMI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597A60CB-119D-4A19-8383-05CC82D05C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDA8E4A-7290-46A7-B401-3AD58137C895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="560" windowWidth="18990" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>g22</t>
-  </si>
-  <si>
     <t>email-Eu-core</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,6 +72,10 @@
   </si>
   <si>
     <t>lpa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LFR_base</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -443,12 +444,13 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -457,21 +459,21 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>0.27916999999999997</v>
@@ -480,10 +482,10 @@
         <v>0.97789999999999999</v>
       </c>
       <c r="D2" s="1">
-        <v>0.66883700000000001</v>
+        <v>0.99317</v>
       </c>
       <c r="E2" s="1">
-        <v>0.71260000000000001</v>
+        <v>0.70794599999999996</v>
       </c>
       <c r="F2" s="1">
         <v>0.61980000000000002</v>
@@ -494,7 +496,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
         <v>0.215975</v>
@@ -503,10 +505,10 @@
         <v>0.90719799999999995</v>
       </c>
       <c r="D3" s="2">
-        <v>0.59533499999999995</v>
+        <v>0.99310200000000004</v>
       </c>
       <c r="E3" s="2">
-        <v>0.56604600000000005</v>
+        <v>0.56347800000000003</v>
       </c>
       <c r="F3" s="2">
         <v>0.55529499999999998</v>
@@ -517,7 +519,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>0.142072</v>
@@ -526,10 +528,10 @@
         <v>0.59489099999999995</v>
       </c>
       <c r="D4" s="2">
-        <v>0.54412400000000005</v>
+        <v>8.8940000000000005E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.20980599999999999</v>
+        <v>0.211841</v>
       </c>
       <c r="F4" s="2">
         <v>0.23033300000000001</v>
@@ -540,7 +542,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>0.21251400000000001</v>
@@ -549,10 +551,10 @@
         <v>0.90719799999999995</v>
       </c>
       <c r="D5" s="2">
-        <v>0.59533499999999995</v>
+        <v>0.99303200000000003</v>
       </c>
       <c r="E5" s="2">
-        <v>0.54483499999999996</v>
+        <v>0.56766899999999998</v>
       </c>
       <c r="F5" s="2">
         <v>0.555724</v>
@@ -563,7 +565,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>0.22950499999999999</v>
@@ -572,10 +574,10 @@
         <v>0.971773</v>
       </c>
       <c r="D6" s="2">
-        <v>0.61774200000000001</v>
+        <v>0.92923999999999995</v>
       </c>
       <c r="E6" s="2">
-        <v>6.8193000000000004E-2</v>
+        <v>0.14547399999999999</v>
       </c>
       <c r="F6" s="2">
         <v>0.60004999999999997</v>
@@ -586,7 +588,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>0.21015300000000001</v>
@@ -595,10 +597,10 @@
         <v>0.83744600000000002</v>
       </c>
       <c r="D7" s="2">
-        <v>0.59503499999999998</v>
+        <v>0.95741200000000004</v>
       </c>
       <c r="E7" s="2">
-        <v>0.478043</v>
+        <v>0.432722</v>
       </c>
       <c r="F7" s="2">
         <v>0.49321599999999999</v>
@@ -609,7 +611,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>0.225137</v>
@@ -617,11 +619,11 @@
       <c r="C8" s="2">
         <v>0.83744600000000002</v>
       </c>
-      <c r="D8" s="1">
-        <v>0.66883700000000001</v>
+      <c r="D8" s="2">
+        <v>0.99303200000000003</v>
       </c>
       <c r="E8" s="2">
-        <v>0.59570299999999998</v>
+        <v>0.55890300000000004</v>
       </c>
       <c r="F8" s="2">
         <v>0.61434999999999995</v>
